--- a/MIM_KPI_updated.xlsx
+++ b/MIM_KPI_updated.xlsx
@@ -6,8 +6,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Methodology" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="KPIs" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -17,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="6">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -53,74 +52,22 @@
     <font>
       <name val="Aptos Narrow"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <b val="1"/>
-      <color rgb="0015803D"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Aptos Narrow"/>
       <sz val="11"/>
     </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <b val="1"/>
-      <color rgb="00B91C1C"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <b val="1"/>
-      <color rgb="00B45309"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <i val="1"/>
-      <color rgb="009CA3AF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <i val="1"/>
-      <color rgb="006B7280"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <b val="1"/>
-      <color rgb="001F2937"/>
-      <sz val="16"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F2937"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FEF3E7"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -128,26 +75,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00D1D5DB"/>
-      </left>
-      <right style="thin">
-        <color rgb="00D1D5DB"/>
-      </right>
-      <top style="thin">
-        <color rgb="00D1D5DB"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00D1D5DB"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -164,63 +97,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -619,993 +497,692 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="13.81640625" customWidth="1" min="1" max="1"/>
+    <col width="14.453125" customWidth="1" min="2" max="2"/>
+    <col width="17.08984375" customWidth="1" min="3" max="3"/>
+    <col width="13.54296875" customWidth="1" min="4" max="4"/>
+    <col width="15.26953125" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>MIM KPI Assessment — Consultant Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="40" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>Assessor</t>
-        </is>
-      </c>
-      <c r="B2" s="8" t="inlineStr">
-        <is>
-          <t>Consultant review of Wave 1 MIM Dashboard</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="40" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>September 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="40" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>servicenow-incidents-* (Elastic index)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Fields verified present</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>priority, priority_name, ci.number, ci.name, ci.support_group.l2.name, business_service.name, assignment_group.name, number, short_description, opened_at, resolved_at, closed_at, contact_type, ci.priority.keyword</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="40" customHeight="1">
-      <c r="A6" s="7" t="inlineStr"/>
-      <c r="B6" s="8" t="inlineStr"/>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>Legend</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>Consultant Verdict column (F)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="40" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>ACHIEVED</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>KPI is built in the enhanced dashboard OR the prototype panel already implements it correctly. Green.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="40" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>NOT ACHIEVABLE</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>The formula requires a field that does not exist in the current data. Column G names the remedy. Red.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="40" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Fix N bugs</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>KPI is achieved but the current implementation has issues that were corrected in the enhanced dashboard. Amber.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="40" customHeight="1">
-      <c r="A11" s="7" t="inlineStr"/>
-      <c r="B11" s="8" t="inlineStr"/>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>Deliverables</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="inlineStr"/>
-    </row>
-    <row r="13" ht="40" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>mim-dashboard-enhanced.ndjson (13 panels, import via Stack Management)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="40" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Instructions</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>docs/mim-dashboard-instructions.md (step-by-step offshore build guide)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="40" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>Review page</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>https://claude.ai/code/artifact/6b2f79a3-c74a-4327-8de8-eb38319ebf1c</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
-  <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="32" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
+    <row r="1" ht="58" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>KPI</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>What it measures</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Typical calculation criteria</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>Benefits</t>
         </is>
       </c>
-      <c r="E1" s="10" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
-      <c r="F1" s="10" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>Consultant Verdict</t>
         </is>
       </c>
-      <c r="G1" s="10" t="inlineStr">
-        <is>
-          <t>How to Achieve (ES|QL / KQL / Remedy)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="60" customHeight="1">
-      <c r="A2" s="11" t="inlineStr">
+    </row>
+    <row r="2" ht="72.5" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t># Active Major Incidents</t>
         </is>
       </c>
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>Operational load</t>
         </is>
       </c>
-      <c r="C2" s="12" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>incident.status:active AND severity:major</t>
         </is>
       </c>
-      <c r="D2" s="12" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>Better visibility + faster staffing</t>
         </is>
       </c>
-      <c r="E2" s="12" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>Pasted to the dashboard</t>
         </is>
       </c>
-      <c r="F2" s="13" t="inlineStr">
-        <is>
-          <t>ACHIEVED (fix field mismatch)</t>
-        </is>
-      </c>
-      <c r="G2" s="14" t="inlineStr">
-        <is>
-          <t>Existing panel filters on ci.priority.keyword:("1" OR "2"). Change to priority IN (1,2) for consistency with all other panels.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="60" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>Agree — already achieved in original dashboard (Active Major Incident tile).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="58" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>MTTA</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Speed to first acknowledge</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>avg(ack_time - detect_time)</t>
         </is>
       </c>
-      <c r="D3" s="12" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Shorter damage window</t>
         </is>
       </c>
-      <c r="E3" s="12" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Can not be achived</t>
         </is>
       </c>
-      <c r="F3" s="15" t="inlineStr">
-        <is>
-          <t>NOT ACHIEVABLE — agree</t>
-        </is>
-      </c>
-      <c r="G3" s="14" t="inlineStr">
-        <is>
-          <t>Field acknowledged_at is not present. Remedy: ServiceNow Business Rule captures sys_updated_on when Acknowledge is clicked into u_acknowledged_at; add field to Elastic integration; then DATE_DIFF("minutes", opened_at, u_acknowledged_at).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>Agree — not achievable. Field 'acknowledged_at' is not present in the incidents index.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="72.5" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>TTD (Declare Major)</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Speed to escalate</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>avg(declare_time - detect_time)</t>
         </is>
       </c>
-      <c r="D4" s="12" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Consistent “major” activation</t>
         </is>
       </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Can not be achived</t>
         </is>
       </c>
-      <c r="F4" s="15" t="inlineStr">
-        <is>
-          <t>NOT ACHIEVABLE — agree</t>
-        </is>
-      </c>
-      <c r="G4" s="14" t="inlineStr">
-        <is>
-          <t>Field major_declared_at is not present. Remedy: ServiceNow Business Rule captures sys_updated_on when major_incident_state changes to Candidate/Accepted into u_major_declared_at; export via integration.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>Agree — not achievable. Field 'major_declared_at' is not present in the incidents index.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="87" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>MTTR</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Speed to recover</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>avg(resolve_time - declare_time) (or resolve - declare)</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Higher availability + fewer repeat incidents</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Pasted to the dashboard</t>
         </is>
       </c>
-      <c r="F5" s="16" t="inlineStr">
-        <is>
-          <t>ACHIEVED (fix 3 bugs)</t>
-        </is>
-      </c>
-      <c r="G5" s="14" t="inlineStr">
-        <is>
-          <t>Fix (a) AVG → MEDIAN to resist outliers; (b) remove hardcoded ci.number IN list — scope by CI control instead; (c) format Duration output as hours. Query: STATS mttr = MEDIAN(DATE_DIFF("minutes", opened_at, resolved_at))</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Agree — already achieved in original dashboard (MTTR ES|QL tile). Use MEDIAN not AVG.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="72.5" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Time to Stabilize (optional if you track it)</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>How fast mitigation makes system stable</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>avg(stable_time - declare_time)</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Reduces oscillation and re-breaks</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Can not be achived</t>
         </is>
       </c>
-      <c r="F6" s="15" t="inlineStr">
-        <is>
-          <t>NOT ACHIEVABLE — agree</t>
-        </is>
-      </c>
-      <c r="G6" s="14" t="inlineStr">
-        <is>
-          <t>Field stabilized_at is not present. Remedy: add custom workflow step in ServiceNow that writes u_stabilized_at when system-stable checkbox is set; export via integration.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>Agree — not achievable. Field 'stabilized_at' is not present.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="72.5" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Incidents by Service/Team</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Where pain concentrates</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>count(incident.id) group by service/team</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Prioritizes engineering work</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Pasted to the dashboard</t>
         </is>
       </c>
-      <c r="F7" s="13" t="inlineStr">
-        <is>
-          <t>ACHIEVED (correct)</t>
-        </is>
-      </c>
-      <c r="G7" s="14" t="inlineStr">
-        <is>
-          <t>Existing datatable groups by ci.name + ci.support_group.l2.name with P1–P5 columns. No change needed. In enhanced dashboard rebuilt as ES|QL for cleaner maintenance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>Agree — already achieved in original dashboard (Incidents by Service/Team datatable).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="101.5" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>SLO Impact Rate</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Reliability/business impact</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>count(slo.breached=true)/count(major incidents)</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Ties MIM performance to objectives</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>No Incidents created on SLO (So can not be achived)</t>
         </is>
       </c>
-      <c r="F8" s="15" t="inlineStr">
-        <is>
-          <t>NOT ACHIEVABLE — agree</t>
-        </is>
-      </c>
-      <c r="G8" s="14" t="inlineStr">
-        <is>
-          <t>No slo.breached field in servicenow-incidents-*. Remedy: enable Elastic SLO feature (Platinum licence); define per-app SLOs; use Transform to denormalize slo.breached onto incidents via time overlap.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>Agree — not achievable. No slo.breached field. Requires Elastic SLO feature.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="101.5" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Recurrence Rate</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Learning effectiveness</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>count(signature repeated within X days)/count(incidents)</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Prevents repeated firefighting</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>Can be achived</t>
         </is>
       </c>
-      <c r="F9" s="13" t="inlineStr">
-        <is>
-          <t>ACHIEVED (new — built)</t>
-        </is>
-      </c>
-      <c r="G9" s="14" t="inlineStr">
-        <is>
-          <t>Rate = COUNT(CIs with &gt;1 P1/P2 incident) / COUNT(distinct CIs with any P1/P2 incident). ES|QL: STATS n=COUNT(*) BY ci.name | STATS repeat=COUNT(CASE(n&gt;1,1,null)), total=COUNT(*) | EVAL rate=ROUND(repeat/total*100,1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>Agree — achievable. Not yet in original dashboard; group P1/P2 by ci.name and compute repeat_cis / total_cis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="87" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>RCA Timeliness (if you store RCA fields)</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>Compliance &amp; learning cadence</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>% rca_submitted_time &lt;= rca_due_time</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>Improves governance + knowledge sharing</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Can not be achived</t>
         </is>
       </c>
-      <c r="F10" s="15" t="inlineStr">
-        <is>
-          <t>NOT ACHIEVABLE — agree</t>
-        </is>
-      </c>
-      <c r="G10" s="14" t="inlineStr">
-        <is>
-          <t>No rca_submitted_at or rca_due_at. Remedy: index ServiceNow problem table via integration; add u_rca_submitted_at and u_rca_due_at fields; join to incidents via problem.related_incident.number.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>Agree — not achievable. No RCA fields on incidents index.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="101.5" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Action Closure Rate</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>Execution effectiveness</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>avg(closed_rate) or % actions closed</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>Ensures RCA leads to real fixes</t>
         </is>
       </c>
-      <c r="E11" s="17" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>Link - https://kibana-prod.gcp.cna.com/app/r/s/tdYZk</t>
         </is>
       </c>
-      <c r="F11" s="13" t="inlineStr">
-        <is>
-          <t>ACHIEVED (new — built as Closure Rate %)</t>
-        </is>
-      </c>
-      <c r="G11" s="14" t="inlineStr">
-        <is>
-          <t>Proxy = COUNT(resolved_at) / COUNT(*) * 100 filtered to priority IN (1,2). External link tdYZk becomes redundant.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" s="18" t="inlineStr">
-        <is>
-          <t>(blank row in source)</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="n"/>
-      <c r="C12" s="12" t="n"/>
-      <c r="D12" s="12" t="n"/>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>Agree — achievable. Not yet in original dashboard; COUNT(resolved_at) / COUNT(*).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="29" customHeight="1">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>Can be achived</t>
         </is>
       </c>
-      <c r="F12" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G12" s="19" t="inlineStr">
-        <is>
-          <t>Row appears blank in source spreadsheet; verdict text sits alone in column E. Recommend deleting or filling in.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
+    </row>
+    <row r="13" ht="101.5" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Avg Time-to-Close RCA Actions (optional)</t>
         </is>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>Speed from insight to change</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>avg(action_closed_time - action_created_time)</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>Faster risk reduction</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>If It's related to MTTR then this is repeatative KIP's</t>
         </is>
       </c>
-      <c r="F13" s="15" t="inlineStr">
-        <is>
-          <t>NOT ACHIEVABLE — redundant with MTTR</t>
-        </is>
-      </c>
-      <c r="G13" s="14" t="inlineStr">
-        <is>
-          <t>Without a separate problem/task index, this is arithmetically identical to MTTR. Skip unless RCA action records are indexed separately.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>Agree — redundant with MTTR when computed from the same opened_at / resolved_at fields.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="101.5" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Impact (Affected Users/Requests) (optional)</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>Customer cost</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>sum(impact.estimated_affected_users)</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>Better severity prioritization</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>If It's related to MTTR then this is repeatative KIP's</t>
         </is>
       </c>
-      <c r="F14" s="15" t="inlineStr">
-        <is>
-          <t>NOT ACHIEVABLE — field missing</t>
-        </is>
-      </c>
-      <c r="G14" s="14" t="inlineStr">
-        <is>
-          <t>No impact.estimated_affected_users field in the index. Would require ServiceNow field capturing user-impact count on each incident, exported to Elastic.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" s="20" t="inlineStr">
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>Agree — not achievable. No impact.estimated_affected_users field.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Incident Volume Over Time</t>
         </is>
       </c>
-      <c r="B15" s="21" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>MIM workload trend</t>
         </is>
       </c>
-      <c r="C15" s="21" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>count(incident) grouped by day and priority</t>
         </is>
       </c>
-      <c r="D15" s="21" t="inlineStr">
-        <is>
-          <t>Detects volume spikes and seasonal patterns; early signal for capacity planning</t>
-        </is>
-      </c>
-      <c r="E15" s="22" t="inlineStr">
-        <is>
-          <t>New (added by consultant review)</t>
-        </is>
-      </c>
-      <c r="F15" s="23" t="inlineStr">
-        <is>
-          <t>ACHIEVED — built</t>
-        </is>
-      </c>
-      <c r="G15" s="21" t="inlineStr">
-        <is>
-          <t>ES|QL: FROM servicenow-incidents-* | STATS c = COUNT(*) BY bucket = DATE_TRUNC(1 day, @timestamp), priority | SORT bucket ASC</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" s="20" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>Detects volume spikes and seasonal patterns</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>New — recommended</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>Achievable. Not yet in original dashboard. ES|QL: STATS c = COUNT(*) BY bucket = DATE_TRUNC(1 day, @timestamp), priority.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>Open Incident Ageing</t>
         </is>
       </c>
-      <c r="B16" s="21" t="inlineStr">
-        <is>
-          <t>Live queue health — unresolved P1/P2 by age</t>
-        </is>
-      </c>
-      <c r="C16" s="21" t="inlineStr">
-        <is>
-          <t>list all incidents where resolved_at IS NULL, compute age_hours = NOW() - opened_at</t>
-        </is>
-      </c>
-      <c r="D16" s="21" t="inlineStr">
-        <is>
-          <t>Catches SLA-breach risk before it happens (P1 &gt; 4h, P2 &gt; 24h are breach-risk)</t>
-        </is>
-      </c>
-      <c r="E16" s="22" t="inlineStr">
-        <is>
-          <t>New (added by consultant review)</t>
-        </is>
-      </c>
-      <c r="F16" s="23" t="inlineStr">
-        <is>
-          <t>ACHIEVED — built</t>
-        </is>
-      </c>
-      <c r="G16" s="21" t="inlineStr">
-        <is>
-          <t>ES|QL: FROM servicenow-incidents-* | WHERE priority IN (1,2) AND resolved_at IS NULL | EVAL age_hours = DATE_DIFF("hours", opened_at, NOW()) | KEEP number, ci.name, priority, age_hours, assignment_group.name | SORT age_hours DESC</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" s="20" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Live queue health for unresolved P1/P2</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>list where resolved_at IS NULL; age = NOW() - opened_at</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>Catches SLA-breach risk before it happens</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>New — recommended</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>Achievable. Not yet in original dashboard. ES|QL: WHERE priority IN (1,2) AND resolved_at IS NULL | EVAL age_hours = DATE_DIFF("hours", opened_at, NOW()).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>Closure Rate %</t>
         </is>
       </c>
-      <c r="B17" s="21" t="inlineStr">
-        <is>
-          <t>Burn-down: what % of P1/P2 incidents opened in the window are resolved</t>
-        </is>
-      </c>
-      <c r="C17" s="21" t="inlineStr">
-        <is>
-          <t>count(resolved_at IS NOT NULL) / count(*) filtered to priority IN (1,2)</t>
-        </is>
-      </c>
-      <c r="D17" s="21" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Burn-down: % of P1/P2 opened in window that are resolved</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>count(resolved_at IS NOT NULL) / count(*) filtered to P1/P2</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>Detects queue growth before headcount reports it</t>
         </is>
       </c>
-      <c r="E17" s="22" t="inlineStr">
-        <is>
-          <t>New (added by consultant review)</t>
-        </is>
-      </c>
-      <c r="F17" s="23" t="inlineStr">
-        <is>
-          <t>ACHIEVED — built</t>
-        </is>
-      </c>
-      <c r="G17" s="21" t="inlineStr">
-        <is>
-          <t>ES|QL: FROM servicenow-incidents-* | WHERE priority IN (1,2) | STATS total = COUNT(*), closed = COUNT(resolved_at) | EVAL rate = ROUND(closed/total*100.0, 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" s="20" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>New — recommended</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>Achievable. Not yet in original dashboard. ES|QL: STATS total = COUNT(*), closed = COUNT(resolved_at) | EVAL rate = closed/total*100.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>Detection Source Ratio</t>
         </is>
       </c>
-      <c r="B18" s="21" t="inlineStr">
-        <is>
-          <t>Proactive (monitoring) vs. reactive (phone/email/self-service) reporting mix</t>
-        </is>
-      </c>
-      <c r="C18" s="21" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Proactive (monitoring) vs. reactive (phone/email) reporting mix</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>count(*) grouped by contact_type</t>
         </is>
       </c>
-      <c r="D18" s="21" t="inlineStr">
-        <is>
-          <t>Monitoring-dominant → mature ops. Phone/email-dominant → alerting coverage gaps</t>
-        </is>
-      </c>
-      <c r="E18" s="22" t="inlineStr">
-        <is>
-          <t>New (added by consultant review)</t>
-        </is>
-      </c>
-      <c r="F18" s="23" t="inlineStr">
-        <is>
-          <t>ACHIEVED — built</t>
-        </is>
-      </c>
-      <c r="G18" s="21" t="inlineStr">
-        <is>
-          <t>ES|QL: FROM servicenow-incidents-* | STATS n = COUNT(*) BY contact_type | SORT n DESC</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" s="20" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Monitoring-dominant = mature ops; phone/email dominant = alerting gaps</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>New — recommended</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>Achievable. Not yet in original dashboard. ES|QL: STATS n = COUNT(*) BY contact_type.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>Top Affected CIs (All Priorities)</t>
         </is>
       </c>
-      <c r="B19" s="21" t="inlineStr">
-        <is>
-          <t>Most-incident-generating CIs across every severity, not just P1/P2</t>
-        </is>
-      </c>
-      <c r="C19" s="21" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Most-incident-generating CIs across every severity</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>count(incident) grouped by ci.name, all priorities</t>
         </is>
       </c>
-      <c r="D19" s="21" t="inlineStr">
-        <is>
-          <t>Surfaces systemic issues that appear in P3/P4 before escalating to P1/P2</t>
-        </is>
-      </c>
-      <c r="E19" s="22" t="inlineStr">
-        <is>
-          <t>New (added by consultant review)</t>
-        </is>
-      </c>
-      <c r="F19" s="23" t="inlineStr">
-        <is>
-          <t>ACHIEVED — built</t>
-        </is>
-      </c>
-      <c r="G19" s="21" t="inlineStr">
-        <is>
-          <t>ES|QL: FROM servicenow-incidents-* | STATS total = COUNT(*) BY ci.name | SORT total DESC | LIMIT 15</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" s="20" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>Surfaces systemic issues appearing in P3/P4 before escalating</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>New — recommended</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>Achievable. Not yet in original dashboard. ES|QL: STATS total = COUNT(*) BY ci.name | SORT total DESC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>Business Service Impact</t>
         </is>
       </c>
-      <c r="B20" s="21" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>Which business services carry the most major incidents</t>
         </is>
       </c>
-      <c r="C20" s="21" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>count(incident where priority IN (1,2)) grouped by business_service.name</t>
         </is>
       </c>
-      <c r="D20" s="21" t="inlineStr">
-        <is>
-          <t>Ties MIM load to business capability; supports service-level conversations with stakeholders</t>
-        </is>
-      </c>
-      <c r="E20" s="22" t="inlineStr">
-        <is>
-          <t>New (added by consultant review)</t>
-        </is>
-      </c>
-      <c r="F20" s="23" t="inlineStr">
-        <is>
-          <t>ACHIEVED — built</t>
-        </is>
-      </c>
-      <c r="G20" s="21" t="inlineStr">
-        <is>
-          <t>ES|QL: FROM servicenow-incidents-* | WHERE priority IN (1,2) | STATS n = COUNT(*) BY business_service.name | SORT n DESC | LIMIT 15</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" s="20" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Ties MIM load to business capability; supports stakeholder conversations</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>New — recommended</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>Achievable. Not yet in original dashboard. ES|QL: WHERE priority IN (1,2) | STATS n = COUNT(*) BY business_service.name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>Assignment Group Load</t>
         </is>
       </c>
-      <c r="B21" s="21" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>Which support teams handle the largest MIM volume</t>
         </is>
       </c>
-      <c r="C21" s="21" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>count(*) grouped by assignment_group.name filtered to major incidents</t>
         </is>
       </c>
-      <c r="D21" s="21" t="inlineStr">
-        <is>
-          <t>Detects team overload; supports staffing and workload rebalancing</t>
-        </is>
-      </c>
-      <c r="E21" s="22" t="inlineStr">
-        <is>
-          <t>New (added by consultant review)</t>
-        </is>
-      </c>
-      <c r="F21" s="23" t="inlineStr">
-        <is>
-          <t>ACHIEVED — built</t>
-        </is>
-      </c>
-      <c r="G21" s="21" t="inlineStr">
-        <is>
-          <t>ES|QL: FROM servicenow-incidents-* | WHERE priority IN (1,2) | STATS n = COUNT(*) BY assignment_group.name | SORT n DESC | LIMIT 15</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" s="20" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>Detects team overload; supports staffing rebalancing</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>New — recommended</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>Achievable. Not yet in original dashboard. ES|QL: WHERE priority IN (1,2) | STATS n = COUNT(*) BY assignment_group.name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>Incident Backlog Burn Rate</t>
         </is>
       </c>
-      <c r="B22" s="21" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>Net rate at which the open MIM queue shrinks per day</t>
         </is>
       </c>
-      <c r="C22" s="21" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>(count(resolved_at in period) - count(opened_at in period)) per day</t>
         </is>
       </c>
-      <c r="D22" s="21" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>Leading indicator of whether the team is keeping up</t>
         </is>
       </c>
-      <c r="E22" s="22" t="inlineStr">
-        <is>
-          <t>New (added by consultant review)</t>
-        </is>
-      </c>
-      <c r="F22" s="24" t="inlineStr">
-        <is>
-          <t>ACHIEVABLE — future iteration</t>
-        </is>
-      </c>
-      <c r="G22" s="21" t="inlineStr">
-        <is>
-          <t>Two ES|QL panels stacked: OPENED per day and RESOLVED per day. Formula in a Vega custom viz: RESOLVED - OPENED = burn rate.</t>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>New — recommended (future iteration)</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>Achievable with a two-stat combination panel; not yet in original dashboard.</t>
         </is>
       </c>
     </row>

--- a/MIM_KPI_updated.xlsx
+++ b/MIM_KPI_updated.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="13.81640625" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,7 @@
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
-          <t>Agree — already achieved in original dashboard (Active Major Incident tile).</t>
+          <t>Achieved in original dashboard (Active Major Incident tile), BUT needs correction: filter uses 'ci.priority.keyword' — should be 'priority' to match the field used by every other panel. Enhanced dashboard fixes this.</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>Agree — already achieved in original dashboard (MTTR ES|QL tile). Use MEDIAN not AVG.</t>
+          <t>Achieved in original dashboard (MTTR ES|QL tile), BUT needs 3 corrections: (1) uses AVG — should be MEDIAN (outliers skew average heavily); (2) hardcodes 10 ci.number values in WHERE clause — should be dynamic (use CI filter control); (3) displays raw minutes — should format as hours. Enhanced dashboard fixes all 3.</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>Agree — already achieved in original dashboard (Incidents by Service/Team datatable).</t>
+          <t>Achieved in original dashboard (Incidents by Service/Team datatable). No correction needed; enhanced dashboard rebuilds as ES|QL for cleaner maintenance.</t>
         </is>
       </c>
     </row>
@@ -791,7 +791,7 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>Agree — achievable. Not yet in original dashboard; group P1/P2 by ci.name and compute repeat_cis / total_cis.</t>
+          <t>Agree — achievable. Not yet in original dashboard; group P1/P2 by ci.name and compute repeats / total_cis * 100.</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>Agree — achievable. Not yet in original dashboard; COUNT(resolved_at) / COUNT(*).</t>
+          <t>Agree — achievable. Not yet in original dashboard; COUNT(resolved_at) / COUNT(*) * 100.</t>
         </is>
       </c>
     </row>
@@ -1183,6 +1183,38 @@
       <c r="F22" s="7" t="inlineStr">
         <is>
           <t>Achievable with a two-stat combination panel; not yet in original dashboard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Long-Open P1/P2 Count (&gt;24h)</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Count of open major incidents older than 24 hours</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>count(*) where priority IN (1,2) AND resolved_at IS NULL AND age_hours &gt; 24</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>At-a-glance count of SLA-breach candidates without scanning the ageing table</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>New — recommended</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>Achievable. Not yet in original dashboard. ES|QL: WHERE priority IN (1,2) AND resolved_at IS NULL | EVAL age_hours = DATE_DIFF("hours", opened_at, NOW()) | WHERE age_hours &gt; 24 | STATS n = COUNT(*).</t>
         </is>
       </c>
     </row>

--- a/MIM_KPI_updated.xlsx
+++ b/MIM_KPI_updated.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="13.81640625" customWidth="1" min="1" max="1"/>
@@ -538,6 +538,11 @@
           <t>Consultant Verdict</t>
         </is>
       </c>
+      <c r="G1" s="6" t="inlineStr">
+        <is>
+          <t>Update Source</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="72.5" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
@@ -567,7 +572,12 @@
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
-          <t>Achieved in original dashboard (Active Major Incident tile), BUT needs correction: filter uses 'ci.priority.keyword' — should be 'priority' to match the field used by every other panel. Enhanced dashboard fixes this.</t>
+          <t>Achieved in enhanced dashboard v2. Original dashboard filtered on 'ci.priority.keyword' — corrected to 'priority' to match all other panels. v2 keeps the count tile AND adds an 'Active P1/P2 — Pending Action' actionable table (Ticket #, CI Name, Priority, Status, Support Group, Assigned Team, Age, Opened).</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>Original request + Action Items Doc — Update</t>
         </is>
       </c>
     </row>
@@ -599,7 +609,12 @@
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
-          <t>Agree — not achievable. Field 'acknowledged_at' is not present in the incidents index.</t>
+          <t>Not achievable. Field 'acknowledged_at' is not present in the incidents index.</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>Original request</t>
         </is>
       </c>
     </row>
@@ -631,7 +646,12 @@
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>Agree — not achievable. Field 'major_declared_at' is not present in the incidents index.</t>
+          <t>Not achievable. Field 'major_declared_at' is not present in the incidents index.</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>Original request</t>
         </is>
       </c>
     </row>
@@ -663,7 +683,12 @@
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>Achieved in original dashboard (MTTR ES|QL tile), BUT needs 3 corrections: (1) uses AVG — should be MEDIAN (outliers skew average heavily); (2) hardcodes 10 ci.number values in WHERE clause — should be dynamic (use CI filter control); (3) displays raw minutes — should format as hours. Enhanced dashboard fixes all 3.</t>
+          <t>Achieved in enhanced dashboard v2 with 3 corrections applied vs. the original: (1) MEDIAN not AVG; (2) hardcoded CI list removed — scope via CI filter control; (3) formatted as hours. MTTR Trend panel now also splits into two series (P1 vs P2) per the team's action-items review.</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Original request + Action Items Doc — Update</t>
         </is>
       </c>
     </row>
@@ -695,7 +720,12 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>Agree — not achievable. Field 'stabilized_at' is not present.</t>
+          <t>Not achievable. Field 'stabilized_at' is not present.</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>Original request</t>
         </is>
       </c>
     </row>
@@ -727,7 +757,12 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>Achieved in original dashboard (Incidents by Service/Team datatable). No correction needed; enhanced dashboard rebuilds as ES|QL for cleaner maintenance.</t>
+          <t>Achieved in enhanced dashboard v2 (Incidents by CI / Support Team datatable). Now restricted to P1+P2 only per action-items review; P3 column removed.</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Original request + Action Items Doc — Update</t>
         </is>
       </c>
     </row>
@@ -759,7 +794,12 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>Agree — not achievable. No slo.breached field. Requires Elastic SLO feature.</t>
+          <t>Not achievable. No slo.breached field. Requires Elastic SLO feature. NOTE: v2 now includes SLA-target monitoring (Breached / At-Risk / Within tiles + detail table) as a functional substitute — uses ITIL default P1=4h, P2=8h.</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>Original request</t>
         </is>
       </c>
     </row>
@@ -791,7 +831,12 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>Agree — achievable. Not yet in original dashboard; group P1/P2 by ci.name and compute repeats / total_cis * 100.</t>
+          <t>Achieved in enhanced dashboard v2 as a percentage metric tile (repeats / total_cis * 100) plus a companion Repeat Offenders pie chart (was table — converted per action-items review).</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>Original request + Action Items Doc — Update</t>
         </is>
       </c>
     </row>
@@ -823,7 +868,12 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>Agree — not achievable. No RCA fields on incidents index.</t>
+          <t>Not achievable. No RCA fields on incidents index.</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>Original request</t>
         </is>
       </c>
     </row>
@@ -855,7 +905,12 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>Agree — achievable. Not yet in original dashboard; COUNT(resolved_at) / COUNT(*) * 100.</t>
+          <t>Achieved in enhanced dashboard v2 as 'Closure Rate (P1+P2)' tile: COUNT(resolved_at) / COUNT(*) * 100. Team asked to clarify calculation logic — see Note in row (denominator = all P1/P2 in selected time window).</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Original request + Action Items Doc — Clarify</t>
         </is>
       </c>
     </row>
@@ -894,7 +949,12 @@
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>Agree — redundant with MTTR when computed from the same opened_at / resolved_at fields.</t>
+          <t>Not achievable / redundant with MTTR when computed from the same opened_at / resolved_at fields.</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>Original request</t>
         </is>
       </c>
     </row>
@@ -926,7 +986,12 @@
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>Agree — not achievable. No impact.estimated_affected_users field.</t>
+          <t>Not achievable. No impact.estimated_affected_users field.</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>Original request</t>
         </is>
       </c>
     </row>
@@ -953,12 +1018,17 @@
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>New — recommended</t>
+          <t>New (added by consultant review)</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>Achievable. Not yet in original dashboard. ES|QL: STATS c = COUNT(*) BY bucket = DATE_TRUNC(1 day, @timestamp), priority.</t>
+          <t>Achieved in enhanced dashboard v2 (multi-series line by priority). ES|QL: STATS c = COUNT(*) BY bucket = DATE_TRUNC(1 day, @timestamp), priority.</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>Consultant recommendation (previous round)</t>
         </is>
       </c>
     </row>
@@ -985,12 +1055,17 @@
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>New — recommended</t>
+          <t>New (added by consultant review)</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>Achievable. Not yet in original dashboard. ES|QL: WHERE priority IN (1,2) AND resolved_at IS NULL | EVAL age_hours = DATE_DIFF("hours", opened_at, NOW()).</t>
+          <t>Achieved in enhanced dashboard v2 — merged into the 'Active P1/P2 — Pending Action' table per action-items request (single actionable table instead of two similar tables).</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>Consultant recommendation + Action Items Doc — Update</t>
         </is>
       </c>
     </row>
@@ -1017,12 +1092,17 @@
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>New — recommended</t>
+          <t>New (added by consultant review)</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>Achievable. Not yet in original dashboard. ES|QL: STATS total = COUNT(*), closed = COUNT(resolved_at) | EVAL rate = closed/total*100.</t>
+          <t>Achieved in enhanced dashboard v2 as the 'Closure Rate (P1+P2)' tile. Calculation clarified per team review: numerator = COUNT(resolved_at) [non-null resolutions]; denominator = COUNT(*) [all P1/P2 opened in the selected time window, open + closed].</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>Consultant recommendation + Action Items Doc — Clarify</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1129,17 @@
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>New — recommended</t>
+          <t>New (added by consultant review)</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>Achievable. Not yet in original dashboard. ES|QL: STATS n = COUNT(*) BY contact_type.</t>
+          <t>Achieved in enhanced dashboard v2 as a pie chart (converted from table per action-items request).</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>Consultant recommendation + Action Items Doc — Update</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1166,17 @@
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>New — recommended</t>
+          <t>New (added by consultant review)</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>Achievable. Not yet in original dashboard. ES|QL: STATS total = COUNT(*) BY ci.name | SORT total DESC.</t>
+          <t>Achieved in enhanced dashboard v2 as a datatable.</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>Consultant recommendation (previous round)</t>
         </is>
       </c>
     </row>
@@ -1113,12 +1203,17 @@
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>New — recommended</t>
+          <t>New (added by consultant review)</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>Achievable. Not yet in original dashboard. ES|QL: WHERE priority IN (1,2) | STATS n = COUNT(*) BY business_service.name.</t>
+          <t>REMOVED from enhanced dashboard v2 per action-items request (team asked to remove the Business Service Impact panel).</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>Consultant recommendation → REMOVED per Action Items Doc</t>
         </is>
       </c>
     </row>
@@ -1145,12 +1240,17 @@
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>New — recommended</t>
+          <t>New (added by consultant review)</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>Achievable. Not yet in original dashboard. ES|QL: WHERE priority IN (1,2) | STATS n = COUNT(*) BY assignment_group.name.</t>
+          <t>Achieved in enhanced dashboard v2 as a pie chart (converted from table per action-items request).</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>Consultant recommendation + Action Items Doc — Update</t>
         </is>
       </c>
     </row>
@@ -1182,7 +1282,12 @@
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>Achievable with a two-stat combination panel; not yet in original dashboard.</t>
+          <t>Not yet built. Achievable with two paired ES|QL panels (OPENED per day, RESOLVED per day).</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>Consultant recommendation (previous round)</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1314,276 @@
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>New — recommended</t>
+          <t>New (added by consultant review)</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>Achievable. Not yet in original dashboard. ES|QL: WHERE priority IN (1,2) AND resolved_at IS NULL | EVAL age_hours = DATE_DIFF("hours", opened_at, NOW()) | WHERE age_hours &gt; 24 | STATS n = COUNT(*).</t>
+          <t>Achieved in enhanced dashboard v2 as the 'Long-Open P1/P2 (&gt;24h)' tile.</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>Consultant recommendation (previous round)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Active P1/P2 — Pending Action Table</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Live table of open major incidents requiring assignment / investigation / resolution</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>list where priority IN (1,2) AND resolved_at IS NULL; columns: Ticket #, CI Name, Priority, Status, Support Group, Assigned Team, Age (hrs), Opened</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Converts the count tile into an actionable operational view — reviewers can identify tickets pending action without navigating away</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>New — from Action Items Doc</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>Achieved in enhanced dashboard v2 (Row 5). ES|QL: FROM servicenow-incidents-* | WHERE priority IN (1,2) AND resolved_at IS NULL | EVAL age_hours = DATE_DIFF("hours", opened_at, NOW()) | EVAL status_val = "Open (pending action)" | KEEP number, ci.name, priority, status_val, ci.support_group.l2.name, assignment_group.name, age_hours, opened_at | SORT age_hours DESC | LIMIT 100.</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>Action Items Doc — New (from item #1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>MTTR Trend by Priority (P1 vs P2)</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Median MTTR trend, one series per priority (P1 and P2)</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>STATS median_mins = MEDIAN(mins) BY bucket = DATE_TRUNC(1 day, @timestamp), priority</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>Detects whether P1 vs P2 recovery speed is diverging — the two often behave differently</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>New — from Action Items Doc</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>Achieved in enhanced dashboard v2 (Row 4). MTTR Trend panel is now multi-series (split by priority) so P1 and P2 curves render separately.</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>Action Items Doc — New (from item #4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Alert vs Auto-Generated Incidents</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Split of monitoring-detected incidents into 'alert' vs 'auto_generated' contact-type origins</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>count(*) grouped by contact_type WHERE contact_type IN ('alert','auto_generated')</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Reveals which detection channel is driving proactive ticket creation</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>New — from Action Items Doc</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>Achieved in enhanced dashboard v2 (Row 8, pie chart). Uses existing contact_type field values 'alert' and 'auto_generated' — no new field required (validated: both values are present in the index per the imported dashboard screenshot mim3.png).</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>Action Items Doc — New (from item #9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>SLA Breached (Open P1/P2)</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Count of open P1/P2 incidents that have already breached their SLA target</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>count(*) where priority IN (1,2) AND resolved_at IS NULL AND age_hours &gt;= sla_target (P1=4h, P2=8h)</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>Immediate visibility into SLA compliance failure — top-line NOC alarm</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>New — from Action Items Doc</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>Achieved in enhanced dashboard v2 as the 'SLA Breached (Open P1/P2)' tile (Row 2). SLA targets are ITIL defaults; adjust the CASE expression to match the actual SLA agreement.</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>Action Items Doc — New (from item #14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>SLA At Risk (Approaching Breach)</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Open P1/P2 incidents that have consumed &gt;=80% of their SLA time budget</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>count(*) where age_hours &gt;= sla_target * 0.8 AND age_hours &lt; sla_target</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Warning-level indicator — tickets to prioritise before they breach</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>New — from Action Items Doc</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>Achieved in enhanced dashboard v2 as the 'SLA At Risk (&gt;=80% of target)' tile (Row 2).</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>Action Items Doc — New (from item #14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>SLA Within Target</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Open P1/P2 incidents that are currently on-track (below 80% of SLA time budget)</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>count(*) where age_hours &lt; sla_target * 0.8</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>Healthy-queue indicator; completes the SLA Status Overview triad</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>New — from Action Items Doc</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>Achieved in enhanced dashboard v2 as the 'SLA Within Target' tile (Row 2).</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>Action Items Doc — New (from item #14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>SLA Breach Detail Table</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Detail of every open P1/P2 incident with SLA status and time-to/from-target</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>KEEP number, priority, state, assignment_group.name, ci.name, age_hours, sla_target_hrs, sla_status, time_delta_hrs</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>Actionable detail for every SLA-relevant ticket in one place — supports drill-down from the SLA tiles</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>New — from Action Items Doc</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>Achieved in enhanced dashboard v2 (Row 3, full-width datatable). Includes CASE expression for sla_status = 'Breached' / 'At Risk' / 'Within SLA'; time_delta_hrs is +ve when overdue, -ve when time remains. 'State' column emitted via EVAL as 'Open' since panel is filtered to resolved_at IS NULL.</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>Action Items Doc — New (from item #15)</t>
         </is>
       </c>
     </row>

--- a/MIM_KPI_updated.xlsx
+++ b/MIM_KPI_updated.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="13.81640625" customWidth="1" min="1" max="1"/>
@@ -543,6 +543,11 @@
           <t>Update Source</t>
         </is>
       </c>
+      <c r="H1" s="6" t="inlineStr">
+        <is>
+          <t>Addresses Action Item(s)</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="72.5" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
@@ -572,12 +577,17 @@
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
-          <t>Achieved in enhanced dashboard v2. Original dashboard filtered on 'ci.priority.keyword' — corrected to 'priority' to match all other panels. v2 keeps the count tile AND adds an 'Active P1/P2 — Pending Action' actionable table (Ticket #, CI Name, Priority, Status, Support Group, Assigned Team, Age, Opened).</t>
+          <t>Achieved in the enhanced dashboard v2 by the 'Active Major Incidents' metric tile (counts all P1/P2 with resolved_at IS NULL). Original 'Active Major Incident' panel filtered on 'ci.priority.keyword' which drifted from the 'priority' field used by every other panel — corrected to 'priority' for consistency. v2 also adds a companion 'Active P1/P2 — Pending Action' datatable so users can see the underlying tickets.</t>
         </is>
       </c>
       <c r="G2" s="7" t="inlineStr">
         <is>
           <t>Original request + Action Items Doc — Update</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>Item #1</t>
         </is>
       </c>
     </row>
@@ -617,6 +627,11 @@
           <t>Original request</t>
         </is>
       </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="72.5" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
@@ -654,6 +669,11 @@
           <t>Original request</t>
         </is>
       </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="87" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -683,12 +703,17 @@
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>Achieved in enhanced dashboard v2 with 3 corrections applied vs. the original: (1) MEDIAN not AVG; (2) hardcoded CI list removed — scope via CI filter control; (3) formatted as hours. MTTR Trend panel now also splits into two series (P1 vs P2) per the team's action-items review.</t>
+          <t>Achieved in the enhanced dashboard v2 by the 'MTTR (Median, P1+P2)' metric tile and the 'MTTR Trend (Median per day, split by P1 &amp; P2)' line chart. Three corrections applied vs. the original: (1) MEDIAN not AVG; (2) hardcoded CI list removed — scope via the CI filter control; (3) formatted as hours. The MTTR Trend now splits into two series per the team's action-items review.</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
           <t>Original request + Action Items Doc — Update</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Item #4</t>
         </is>
       </c>
     </row>
@@ -728,6 +753,11 @@
           <t>Original request</t>
         </is>
       </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="72.5" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -757,12 +787,17 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>Achieved in enhanced dashboard v2 (Incidents by CI / Support Team datatable). Now restricted to P1+P2 only per action-items review; P3 column removed.</t>
+          <t>Achieved in the enhanced dashboard v2 by the 'Incidents by CI / Support Team (P1+P2 Only)' datatable. Restricted to P1+P2 per action-items review; the P3 column was dropped.</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
           <t>Original request + Action Items Doc — Update</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>Item #5</t>
         </is>
       </c>
     </row>
@@ -794,12 +829,17 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>Not achievable. No slo.breached field. Requires Elastic SLO feature. NOTE: v2 now includes SLA-target monitoring (Breached / At-Risk / Within tiles + detail table) as a functional substitute — uses ITIL default P1=4h, P2=8h.</t>
+          <t>Not achievable via servicenow-incidents-* alone. No 'slo.breached' field. Requires Elastic SLO feature. NOTE: v2 provides a functional substitute via SLA-target monitoring — the 'SLA Breached (Open P1/P2)', 'SLA At Risk (&gt;=80% of target)', and 'SLA Within Target' tiles plus the 'SLA Breach Detail — Open P1/P2 Incidents' datatable. SLA targets are ITIL defaults (P1=4h, P2=8h); adjust the CASE expression to match the actual SLA agreement.</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>Original request</t>
+          <t>Original request (SLA substitute added per Action Items Doc)</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>Items #14, #15 (SLA substitute)</t>
         </is>
       </c>
     </row>
@@ -831,12 +871,17 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>Achieved in enhanced dashboard v2 as a percentage metric tile (repeats / total_cis * 100) plus a companion Repeat Offenders pie chart (was table — converted per action-items review).</t>
+          <t>Achieved in the enhanced dashboard v2 by the 'Recurrence Rate (P1+P2)' metric tile (percentage of CIs with &gt;1 major incident) plus the 'Repeat-Offender CIs (&gt;1 P1/P2 Incident)' pie chart (drill-down detail). The list was converted from a table to a pie per action-items review.</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
           <t>Original request + Action Items Doc — Update</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>Items #6, #7</t>
         </is>
       </c>
     </row>
@@ -868,12 +913,17 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>Not achievable. No RCA fields on incidents index.</t>
+          <t>Not achievable. No RCA fields on the incidents index.</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
           <t>Original request</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -905,12 +955,17 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>Achieved in enhanced dashboard v2 as 'Closure Rate (P1+P2)' tile: COUNT(resolved_at) / COUNT(*) * 100. Team asked to clarify calculation logic — see Note in row (denominator = all P1/P2 in selected time window).</t>
+          <t>Achieved in the enhanced dashboard v2 by the 'Closure Rate (P1+P2)' metric tile: COUNT(resolved_at) / COUNT(*) * 100 filtered to P1+P2. Denominator is all P1+P2 opened in the selected time window (open + closed); numerator is the non-null resolved_at count. Clarified per action-items review.</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
           <t>Original request + Action Items Doc — Clarify</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>Item #2</t>
         </is>
       </c>
     </row>
@@ -957,6 +1012,11 @@
           <t>Original request</t>
         </is>
       </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="101.5" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
@@ -986,12 +1046,17 @@
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>Not achievable. No impact.estimated_affected_users field.</t>
+          <t>Not achievable. No 'impact.estimated_affected_users' field in the index.</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
           <t>Original request</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -1023,12 +1088,17 @@
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>Achieved in enhanced dashboard v2 (multi-series line by priority). ES|QL: STATS c = COUNT(*) BY bucket = DATE_TRUNC(1 day, @timestamp), priority.</t>
+          <t>Achieved in the enhanced dashboard v2 by the 'Incident Volume Over Time (by Priority)' multi-series line chart.</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
           <t>Consultant recommendation (previous round)</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>Item #3 (drill-down applies to this chart)</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1130,17 @@
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>Achieved in enhanced dashboard v2 — merged into the 'Active P1/P2 — Pending Action' table per action-items request (single actionable table instead of two similar tables).</t>
+          <t>Achieved in the enhanced dashboard v2 by the 'Active P1/P2 — Pending Action' datatable — merged with Aging Analysis into a single actionable table per action-items request.</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
           <t>Consultant recommendation + Action Items Doc — Update</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>Items #10, #11 (merged into #1)</t>
         </is>
       </c>
     </row>
@@ -1097,12 +1172,17 @@
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>Achieved in enhanced dashboard v2 as the 'Closure Rate (P1+P2)' tile. Calculation clarified per team review: numerator = COUNT(resolved_at) [non-null resolutions]; denominator = COUNT(*) [all P1/P2 opened in the selected time window, open + closed].</t>
+          <t>Achieved in the enhanced dashboard v2 by the 'Closure Rate (P1+P2)' metric tile. Calculation clarified per action-items review: denominator = all P1+P2 opened in the window; numerator = COUNT(resolved_at) [non-null resolutions].</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
           <t>Consultant recommendation + Action Items Doc — Clarify</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>Item #2</t>
         </is>
       </c>
     </row>
@@ -1134,12 +1214,17 @@
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>Achieved in enhanced dashboard v2 as a pie chart (converted from table per action-items request).</t>
+          <t>Achieved in the enhanced dashboard v2 by the 'Detection Source (All Incidents)' pie chart. Converted from a table per action-items review.</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
           <t>Consultant recommendation + Action Items Doc — Update</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>Item #8</t>
         </is>
       </c>
     </row>
@@ -1171,12 +1256,17 @@
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>Achieved in enhanced dashboard v2 as a datatable.</t>
+          <t>Achieved in the enhanced dashboard v2 by the 'Top Affected CIs (All Priorities)' datatable.</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
           <t>Consultant recommendation (previous round)</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -1208,12 +1298,17 @@
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>REMOVED from enhanced dashboard v2 per action-items request (team asked to remove the Business Service Impact panel).</t>
+          <t>REMOVED from the enhanced dashboard v2 per action-items request (team asked to remove the Business Service Impact panel).</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
           <t>Consultant recommendation → REMOVED per Action Items Doc</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>Item #12</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1340,17 @@
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>Achieved in enhanced dashboard v2 as a pie chart (converted from table per action-items request).</t>
+          <t>Achieved in the enhanced dashboard v2 by the 'Assignment Group Load (P1+P2)' pie chart. Converted from a table per action-items review.</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
           <t>Consultant recommendation + Action Items Doc — Update</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>Item #13</t>
         </is>
       </c>
     </row>
@@ -1282,12 +1382,17 @@
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>Not yet built. Achievable with two paired ES|QL panels (OPENED per day, RESOLVED per day).</t>
+          <t>Not yet built. Achievable with two paired ES|QL panels (OPENED per day and RESOLVED per day, combined in a Vega custom viz).</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
           <t>Consultant recommendation (previous round)</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -1319,12 +1424,17 @@
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>Achieved in enhanced dashboard v2 as the 'Long-Open P1/P2 (&gt;24h)' tile.</t>
+          <t>Achieved in the enhanced dashboard v2 by the 'Long-Open P1/P2 (&gt;24h)' metric tile.</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
           <t>Consultant recommendation (previous round)</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1466,17 @@
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>Achieved in enhanced dashboard v2 (Row 5). ES|QL: FROM servicenow-incidents-* | WHERE priority IN (1,2) AND resolved_at IS NULL | EVAL age_hours = DATE_DIFF("hours", opened_at, NOW()) | EVAL status_val = "Open (pending action)" | KEEP number, ci.name, priority, status_val, ci.support_group.l2.name, assignment_group.name, age_hours, opened_at | SORT age_hours DESC | LIMIT 100.</t>
+          <t>Achieved in the enhanced dashboard v2 by the 'Active P1/P2 — Pending Action' datatable (uses CI Name — not CI Number — and adds Support Group and Status columns per the team request).</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>Action Items Doc — New (from item #1)</t>
+          <t>Action Items Doc — New</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>Item #1</t>
         </is>
       </c>
     </row>
@@ -1393,12 +1508,17 @@
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>Achieved in enhanced dashboard v2 (Row 4). MTTR Trend panel is now multi-series (split by priority) so P1 and P2 curves render separately.</t>
+          <t>Achieved in the enhanced dashboard v2 by the 'MTTR Trend (Median per day, split by P1 &amp; P2)' line chart — now multi-series so P1 and P2 curves render separately.</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>Action Items Doc — New (from item #4)</t>
+          <t>Action Items Doc — New</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>Item #4</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1530,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Split of monitoring-detected incidents into 'alert' vs 'auto_generated' contact-type origins</t>
+          <t>Split of monitoring-detected incidents into 'alert' vs 'auto_generated' origins</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -1430,12 +1550,17 @@
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>Achieved in enhanced dashboard v2 (Row 8, pie chart). Uses existing contact_type field values 'alert' and 'auto_generated' — no new field required (validated: both values are present in the index per the imported dashboard screenshot mim3.png).</t>
+          <t>Achieved in the enhanced dashboard v2 by the 'Alert vs Auto-Generated Incidents' pie chart. Uses existing contact_type field values 'alert' and 'auto_generated' — no new field required (both values are present in the index).</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>Action Items Doc — New (from item #9)</t>
+          <t>Action Items Doc — New</t>
+        </is>
+      </c>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>Item #9</t>
         </is>
       </c>
     </row>
@@ -1467,12 +1592,17 @@
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>Achieved in enhanced dashboard v2 as the 'SLA Breached (Open P1/P2)' tile (Row 2). SLA targets are ITIL defaults; adjust the CASE expression to match the actual SLA agreement.</t>
+          <t>Achieved in the enhanced dashboard v2 by the 'SLA Breached (Open P1/P2)' metric tile. SLA targets are ITIL defaults; adjust the CASE expression to match the actual SLA agreement.</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>Action Items Doc — New (from item #14)</t>
+          <t>Action Items Doc — New</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>Item #14</t>
         </is>
       </c>
     </row>
@@ -1504,12 +1634,17 @@
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>Achieved in enhanced dashboard v2 as the 'SLA At Risk (&gt;=80% of target)' tile (Row 2).</t>
+          <t>Achieved in the enhanced dashboard v2 by the 'SLA At Risk (&gt;=80% of target)' metric tile.</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>Action Items Doc — New (from item #14)</t>
+          <t>Action Items Doc — New</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>Item #14</t>
         </is>
       </c>
     </row>
@@ -1541,12 +1676,17 @@
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>Achieved in enhanced dashboard v2 as the 'SLA Within Target' tile (Row 2).</t>
+          <t>Achieved in the enhanced dashboard v2 by the 'SLA Within Target' metric tile.</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>Action Items Doc — New (from item #14)</t>
+          <t>Action Items Doc — New</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>Item #14</t>
         </is>
       </c>
     </row>
@@ -1578,12 +1718,17 @@
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>Achieved in enhanced dashboard v2 (Row 3, full-width datatable). Includes CASE expression for sla_status = 'Breached' / 'At Risk' / 'Within SLA'; time_delta_hrs is +ve when overdue, -ve when time remains. 'State' column emitted via EVAL as 'Open' since panel is filtered to resolved_at IS NULL.</t>
+          <t>Achieved in the enhanced dashboard v2 by the 'SLA Breach Detail — Open P1/P2 Incidents' datatable. Includes CASE expression for sla_status = 'Breached' / 'At Risk' / 'Within SLA'; time_delta_hrs is +ve when overdue, -ve when time remains. 'State' column emitted via EVAL as 'Open' since panel is filtered to resolved_at IS NULL.</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>Action Items Doc — New (from item #15)</t>
+          <t>Action Items Doc — New</t>
+        </is>
+      </c>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>Item #15</t>
         </is>
       </c>
     </row>

--- a/MIM_KPI_updated.xlsx
+++ b/MIM_KPI_updated.xlsx
@@ -7,6 +7,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Action Items Mapping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -80,7 +81,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -99,6 +100,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1746,4 +1753,478 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Item #</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>Action Item (from docx)</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t># KPIs</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>KPI(s) Addressing It</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="inlineStr">
+        <is>
+          <t>Enhanced Dashboard v2 Panel(s)</t>
+        </is>
+      </c>
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="80" customHeight="1">
+      <c r="A2" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="9" t="inlineStr">
+        <is>
+          <t>Active P1/P2 Panel — enhance to identify incidents requiring action; provide visibility into tickets pending assignment / investigation / resolution; replace CI Number with CI Name; add Support Group and Status columns</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t># Active Major Incidents; Open Incident Ageing (merged into #1); Active P1/P2 — Pending Action Table</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>'Active Major Incidents' metric tile + 'Active P1/P2 — Pending Action' datatable</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>Achieved</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="80" customHeight="1">
+      <c r="A3" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Resolved/Opened Panel — review and clarify calculation logic; confirm whether metric is based on Open P1/P2 only or all P1/P2 within reporting period; update widget definition and tooltip</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Action Closure Rate; Closure Rate %</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>'Closure Rate (P1+P2)' metric tile — denominator = all P1+P2 opened in window; numerator = COUNT(resolved_at)</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>Achieved</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="80" customHeight="1">
+      <c r="A4" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Drill-Down Capability — add drill-down to all widgets containing line graphs; users should click a data point and view underlying incident records</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Incident Volume Over Time; MTTR Trend by Priority (P1 vs P2)</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>'Incident Volume Over Time (by Priority)' and 'MTTR Trend (Median per day, split by P1 &amp; P2)' — Kibana default click-to-filter behaviour applies to both</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>Achieved</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="80" customHeight="1">
+      <c r="A5" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>MTTR Trend (Median P1+P2 Per Day) — implement separate MTTR trends for P1 and P2 (or drill-down showing MTTR tickets)</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>MTTR; MTTR Trend by Priority (P1 vs P2)</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>'MTTR Trend (Median per day, split by P1 &amp; P2)' line chart — multi-series</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>Achieved</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="80" customHeight="1">
+      <c r="A6" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Incidents by CI / Support Team — restrict data to P1 and P2 incidents only</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Incidents by Service/Team</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>'Incidents by CI / Support Team (P1+P2 Only)' datatable — added WHERE priority IN (1,2), dropped P3 column</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>Achieved</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="80" customHeight="1">
+      <c r="A7" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Percentage of CIs with Major Incidents — convert to drill-down enabled widget; add detailed table showing CIs associated with more than one major incident</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>Recurrence Rate</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>'Recurrence Rate (P1+P2)' metric tile + 'Repeat-Offender CIs (&gt;1 P1/P2 Incident)' pie (the drill-down detail)</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>Achieved</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="80" customHeight="1">
+      <c r="A8" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>Repeat Offenders — convert the existing table into a pie chart</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Recurrence Rate</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>'Repeat-Offender CIs (&gt;1 P1/P2 Incident)' pie chart — converted from datatable</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>Achieved</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="80" customHeight="1">
+      <c r="A9" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Detection Source — convert the existing table into a pie chart</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>Detection Source Ratio</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>'Detection Source (All Incidents)' pie chart — converted from datatable</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>Achieved</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="80" customHeight="1">
+      <c r="A10" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Alert vs Auto-Generated Incidents — add new widget between Detection Source and Top Affected CIs showing alert-generated and auto-generated incidents; validate source field</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>Alert vs Auto-Generated Incidents</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>'Alert vs Auto-Generated Incidents' pie chart — uses existing contact_type values 'alert' and 'auto_generated' (both confirmed present in the index; no new field required)</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>Achieved</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="80" customHeight="1">
+      <c r="A11" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Open Incidents — no changes required</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>Open Incident Ageing</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>'Active P1/P2 — Pending Action' datatable (also serves this view)</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>No change needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="80" customHeight="1">
+      <c r="A12" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>Aging Analysis — no changes required</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>Open Incident Ageing</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>'Active P1/P2 — Pending Action' datatable — merged with Aging Analysis into a single actionable table per item #1</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>No change needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="80" customHeight="1">
+      <c r="A13" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Business Service Impact (P1+P2) — remove the Business Service Impact panel</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>Business Service Impact</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>REMOVED from the dashboard</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>Achieved (removed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="80" customHeight="1">
+      <c r="A14" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>Assignment Group Load (P1+P2 Incidents) — change visualization from a table to a pie chart</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>Assignment Group Load</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>'Assignment Group Load (P1+P2)' pie chart — converted from datatable</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>Achieved</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="80" customHeight="1">
+      <c r="A15" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>SLA Monitoring for Open P1/P2 Tickets — add SLA-focused widgets: SLA Breached, SLA At Risk / Will Breach Soon, SLA Status Overview (Within / Approaching / Breached); enable drill-down on all SLA widgets</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>SLO Impact Rate (substitute); SLA Breached (Open P1/P2); SLA At Risk (Approaching Breach); SLA Within Target</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>'SLA Breached (Open P1/P2)' + 'SLA At Risk (&gt;=80% of target)' + 'SLA Within Target' metric tiles. SLA targets are ITIL defaults (P1=4h, P2=8h); adjust the CASE expression to match the actual SLA agreement</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>Achieved</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="80" customHeight="1">
+      <c r="A16" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>SLA Breach Detail View — clicking any SLA-related widget should open a detailed table showing: Incident #, Priority, State, Assigned Group, CI Name, Ticket Age, SLA Target, SLA Status, Time Remaining / Time Overdue</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>SLO Impact Rate (substitute); SLA Breach Detail Table</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>'SLA Breach Detail — Open P1/P2 Incidents' datatable with every requested column. Kibana default click-to-filter satisfies the 'clicking any SLA widget' request</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>Achieved</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/MIM_KPI_updated.xlsx
+++ b/MIM_KPI_updated.xlsx
@@ -1374,7 +1374,7 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>(count(resolved_at in period) - count(opened_at in period)) per day</t>
+          <t>opened_per_day vs resolved_per_day (backlog shrinks when resolved &gt; opened)</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>New — recommended (future iteration)</t>
+          <t>New — recommended</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>Not yet built. Achievable with two paired ES|QL panels (OPENED per day and RESOLVED per day, combined in a Vega custom viz).</t>
+          <t>Achieved in the enhanced dashboard v2 by the 'Backlog Burn Rate — Opened vs Resolved per day (P1+P2)' line chart. Uses ES|QL MV_EXPAND to unpivot each incident into two event rows (opened + resolved) and renders both series on one chart — when the Resolved line sits above Opened, the backlog is shrinking. If MV_EXPAND on an inline array literal is not supported in your Kibana build, split into two side-by-side ES|QL panels: one filtered on opened_at, the other on resolved_at.</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
